--- a/data/availability/projects/madaar-developments/the-hillage.xlsx
+++ b/data/availability/projects/madaar-developments/the-hillage.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1009,7 +1009,6 @@
       <c r="G2" t="n">
         <v>138</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1020,7 +1019,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1066,7 +1065,6 @@
       <c r="G3" t="n">
         <v>190</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1077,7 +1075,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1138,7 +1136,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1199,7 +1197,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1260,7 +1258,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1321,7 +1319,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1382,7 +1380,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1443,7 +1441,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
